--- a/booking_forms/017_romantic_getaway_reservation_form--booking_forms.xlsx
+++ b/booking_forms/017_romantic_getaway_reservation_form--booking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -811,8 +811,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -840,12 +840,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'1_room',_'label':_'1_room'}</t>
+          <t>1_room</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': '1 room', 'label': '1 room'}</t>
+          <t>1 room</t>
         </is>
       </c>
     </row>
@@ -857,12 +857,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'2_rooms',_'label':_'2_rooms'}</t>
+          <t>2_rooms</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': '2 rooms', 'label': '2 rooms'}</t>
+          <t>2 rooms</t>
         </is>
       </c>
     </row>
@@ -874,12 +874,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'vegetarian',_'label':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Vegetarian', 'label': 'Vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'non-vegetarian',_'label':_'non-vegetarian'}</t>
+          <t>non-vegetarian</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Non-vegetarian', 'label': 'Non-vegetarian'}</t>
+          <t>Non-vegetarian</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'private_car',_'label':_'private_car'}</t>
+          <t>private_car</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Private car', 'label': 'Private car'}</t>
+          <t>Private car</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'public_transport',_'label':_'public_transport'}</t>
+          <t>public_transport</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Public transport', 'label': 'Public transport'}</t>
+          <t>Public transport</t>
         </is>
       </c>
     </row>
